--- a/src/main/resources/account/default/BAS-2026---Ideell-forening-stiftelse-och-trossamfund.xlsx
+++ b/src/main/resources/account/default/BAS-2026---Ideell-forening-stiftelse-och-trossamfund.xlsx
@@ -427,6 +427,9 @@
           <t>BAS 2026 - Ideell förening, stiftelse och trossamfund</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +442,9 @@
           <t>EUBAS97</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -451,6 +457,9 @@
           <t>2026</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -461,6 +470,9 @@
       <c r="B4" t="n">
         <v>6</v>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2776,7 +2788,11 @@
           <t>Pågående arbeten, nedlagda kostnader</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>8726</t>
@@ -6361,7 +6377,11 @@
           <t>Kortfristiga lån från kreditinstitut</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
           <t>8740</t>
@@ -6378,7 +6398,11 @@
           <t>Byggnadskreditiv, kortfristig del</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
           <t>8740</t>
@@ -6446,7 +6470,11 @@
           <t>Ej inlösta presentkort</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr"/>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
           <t>8740</t>
@@ -6497,7 +6525,11 @@
           <t>Pågående arbeten, fakturering</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
           <t>8740</t>
@@ -6990,7 +7022,11 @@
           <t>Utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D398" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7007,7 +7043,11 @@
           <t>Utgående moms på försäljning inom Sverige, 25 %</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7024,7 +7064,11 @@
           <t>Utgående moms på egna uttag, 25 %</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7041,7 +7085,11 @@
           <t>Utgående moms för uthyrning, 25 %</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D401" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7058,7 +7106,11 @@
           <t>Utgående moms omvänd betalskyldighet, 25 %</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7075,7 +7127,11 @@
           <t>Utgående moms import av varor, 25 %</t>
         </is>
       </c>
-      <c r="C403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>U1MI</t>
+        </is>
+      </c>
       <c r="D403" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7109,7 +7165,11 @@
           <t>Vilande utgående moms, 25 %</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7143,7 +7203,11 @@
           <t>Utgående moms på försäljning inom Sverige, 12 %</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D407" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7160,7 +7224,11 @@
           <t>Utgående moms på egna uttag, 12 %</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D408" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7194,7 +7262,11 @@
           <t>Utgående moms omvänd betalningsskyldighet 12 %</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D410" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7211,7 +7283,11 @@
           <t>Utgående moms import av varor, 12 %</t>
         </is>
       </c>
-      <c r="C411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>U2MI</t>
+        </is>
+      </c>
       <c r="D411" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7245,7 +7321,11 @@
           <t>Vilande utgående moms, 12 %</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
       <c r="D413" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7279,7 +7359,11 @@
           <t>Utgående moms på försäljning inom Sverige, 6 %</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D415" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7296,7 +7380,11 @@
           <t>Utgående moms på egna uttag, 6 %</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7330,7 +7418,11 @@
           <t>Utgående moms omvänd betalningsskyldighet, 6 %</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D418" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7347,7 +7439,11 @@
           <t>Utgående moms import av varor, 6 %</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>U3MI</t>
+        </is>
+      </c>
       <c r="D419" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7381,7 +7477,11 @@
           <t>Vilande utgående moms, 6 %</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>U3</t>
+        </is>
+      </c>
       <c r="D421" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7398,7 +7498,11 @@
           <t>Ingående moms</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7415,7 +7519,11 @@
           <t>Debiterad ingående moms</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D423" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7432,7 +7540,11 @@
           <t>Debiterad ingående moms i anslutning till frivillig betalningsskyldighet</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D424" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7449,7 +7561,11 @@
           <t>Beräknad ingående moms på förvärv från utlandet</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D425" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7466,7 +7582,11 @@
           <t>Ingående moms på uthyrning</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D426" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7500,7 +7620,11 @@
           <t>Vilande ingående moms</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D428" t="inlineStr">
         <is>
           <t>8743</t>
@@ -7517,7 +7641,11 @@
           <t>Ingående moms, blandad verksamhet</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D429" t="inlineStr">
         <is>
           <t>8743</t>
@@ -9237,7 +9365,11 @@
           <t>Fakturerade kostnader (gruppkonto)</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D529" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9254,7 +9386,11 @@
           <t>Fakturerat emballage</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D530" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9305,7 +9441,11 @@
           <t>Fakturerade frakter</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D533" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9339,7 +9479,11 @@
           <t>Fakturerade frakter, export</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D535" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9356,7 +9500,11 @@
           <t>Fakturerade tull- och  speditionskostnader m.m.</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D536" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9373,7 +9521,11 @@
           <t>Faktureringsavgifter</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D537" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9390,7 +9542,11 @@
           <t>Faktureringsavgifter, EU-land</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="D538" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9407,7 +9563,11 @@
           <t>Faktureringsavgifter, export</t>
         </is>
       </c>
-      <c r="C539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>VTEU</t>
+        </is>
+      </c>
       <c r="D539" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9424,7 +9584,11 @@
           <t>Fakturerade resekostnader</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D540" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9441,7 +9605,11 @@
           <t>Fakturerade kostnader till  koncernföretag</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D541" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9509,7 +9677,11 @@
           <t>Fakturerade kostnader till  intresseföretag, gemensamt styrda företag och övriga företag som det finns ett ägarintresse i</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D545" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9526,7 +9698,11 @@
           <t>Övriga fakturerade kostnader</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9543,7 +9719,11 @@
           <t>Rörelsens sidointäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D547" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9560,7 +9740,11 @@
           <t>Försäljning av material</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D548" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9645,7 +9829,11 @@
           <t>Tillfällig uthyrning av personal</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D553" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9764,7 +9952,11 @@
           <t>Övriga sidointäkter</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D560" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9781,7 +9973,11 @@
           <t>Intäktskorrigeringar (gruppkonto)</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D561" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9798,7 +9994,11 @@
           <t>Ofördelade intäktsreduktioner</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr"/>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D562" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9815,7 +10015,11 @@
           <t>Lämnade rabatter</t>
         </is>
       </c>
-      <c r="C563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D563" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9887,7 +10091,11 @@
           <t>Punktskatter</t>
         </is>
       </c>
-      <c r="C567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D567" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9938,7 +10146,11 @@
           <t>Övriga intäktskorrigeringar</t>
         </is>
       </c>
-      <c r="C570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D570" t="inlineStr">
         <is>
           <t>8653</t>
@@ -9989,7 +10201,11 @@
           <t>Aktiverat arbete (omkostnader)</t>
         </is>
       </c>
-      <c r="C573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D573" t="inlineStr">
         <is>
           <t>8654</t>
@@ -10023,7 +10239,11 @@
           <t>Övriga rörelseintäkter (gruppkonto)</t>
         </is>
       </c>
-      <c r="C575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>MP1</t>
+        </is>
+      </c>
       <c r="D575" t="inlineStr">
         <is>
           <t>8654</t>
@@ -10210,7 +10430,11 @@
           <t>Återvunna, tidigare avskrivna  kundfordringar</t>
         </is>
       </c>
-      <c r="C586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D586" t="inlineStr">
         <is>
           <t>8654</t>
@@ -10312,7 +10536,11 @@
           <t>Erhållna offentliga bidrag</t>
         </is>
       </c>
-      <c r="C592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
           <t>8654</t>
@@ -10414,7 +10642,11 @@
           <t>Övriga ersättningar, bidrag och  intäkter</t>
         </is>
       </c>
-      <c r="C598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>MF</t>
+        </is>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
           <t>8654</t>
